--- a/Data/Prueba.xlsx
+++ b/Data/Prueba.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Unnamed: 6</t>
+          <t>INTENTOS</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -572,7 +572,9 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>LOGD590706HASPNV00</t>
@@ -609,7 +611,7 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-05-18 10:49:35</t>
+          <t>2026-06-03 11:34:56</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -627,7 +629,9 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>VIJG670818MASLMB03</t>
@@ -662,7 +666,7 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-05-20 08:22:07</t>
+          <t>2026-06-03 11:16:51</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>

--- a/Data/Prueba.xlsx
+++ b/Data/Prueba.xlsx
@@ -573,7 +573,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-06-03 11:34:56</t>
+          <t>2026-06-03 12:03:47</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>

--- a/Data/Prueba.xlsx
+++ b/Data/Prueba.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA4"/>
+  <dimension ref="A1:AB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,107 +461,112 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>v</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>CURP</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>NSS</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>CORREO</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>CLIENTE</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>COSTO SEGURO</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>HONORARIOS</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>NUMERO TELEFONICO</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>RFC</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>NUMERO</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>WORD</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>IntentosCaptcha</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Archivo</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>CarpetaPDF</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>UltimaActualizacion</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>CARPETAPDF</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>MENSAJE</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>INTENTOS</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>CURP</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>NSS</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>CORREO</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>CLIENTE</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>COSTO SEGURO</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>HONORARIOS</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>NUMERO TELEFONICO</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>RFC</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>NUMERO</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>WORD</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>IntentosCaptcha</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Archivo</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>CarpetaPDF</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>UltimaActualizacion</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>CARPETAPDF</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>MENSAJE</t>
         </is>
       </c>
     </row>
@@ -572,9 +577,7 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
-        <v>3</v>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>LOGD590706HASPNV00</t>
@@ -604,14 +607,18 @@
         <v>4494295044</v>
       </c>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>C:\Users\Dembe\Proyects\Python\AsistenteIMSS\Data\pdf\Juan Pablo Salinas\Juan Pablo Salinas_Y242PY9C4CBY2CLBZ64950000RPN00019RE00000000000000RV7Z.pdf</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-06-03 12:03:47</t>
+          <t>2026-06-11 13:51:22</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -621,6 +628,9 @@
         </is>
       </c>
       <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -629,9 +639,7 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>VIJG670818MASLMB03</t>
@@ -659,14 +667,18 @@
         <v>4494295044</v>
       </c>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>C:\Users\Dembe\Proyects\Python\AsistenteIMSS\Data\pdf\Gabriela Villanueva\Gabriela Villanueva_Y242PY9C4CBY2BFJO64950000RPN00019RE00000000000000126D.pdf</t>
+        </is>
+      </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-06-03 11:16:51</t>
+          <t>2026-06-11 14:11:13</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -676,6 +688,9 @@
         </is>
       </c>
       <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -710,14 +725,18 @@
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>C:\Users\Dembe\Proyects\Python\AsistenteIMSS\Data\pdf\J Carmen\J Carmen_B291BZQI4CBY22NLD64950000RPN00019RE00000000000000127L.pdf</t>
+        </is>
+      </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-05-20 08:23:42</t>
+          <t>2026-06-11 13:52:22</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -727,6 +746,9 @@
         </is>
       </c>
       <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
